--- a/output/pdf_financials_xlsx/MKT.xlsx
+++ b/output/pdf_financials_xlsx/MKT.xlsx
@@ -1273,40 +1273,40 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.058988</v>
+        <v>-0.058988</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.172846</v>
+        <v>-0.172846</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.919814</v>
+        <v>-0.919814</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.496136</v>
+        <v>-2.496136</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.813302</v>
+        <v>-1.813302</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.442481</v>
+        <v>-2.442481</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.384723</v>
+        <v>-1.384723</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.648234</v>
+        <v>-1.648234</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.003025</v>
+        <v>-2.003025</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>2.416189</v>
+        <v>-2.416189</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.911632</v>
+        <v>-1.911632</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.684791</v>
+        <v>-0.684791</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-4.764727</v>
@@ -1573,40 +1573,40 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.058988</v>
+        <v>-0.058988</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.172846</v>
+        <v>-0.172846</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.919814</v>
+        <v>-0.919814</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.496136</v>
+        <v>-2.496136</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.813302</v>
+        <v>-1.813302</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.442481</v>
+        <v>-2.442481</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.384723</v>
+        <v>-1.384723</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.648234</v>
+        <v>-1.648234</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.003025</v>
+        <v>-2.003025</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.416189</v>
+        <v>-2.416189</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.911632</v>
+        <v>-1.911632</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.684791</v>
+        <v>-0.684791</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-4.764727</v>
@@ -1747,40 +1747,40 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.058988</v>
+        <v>-0.058988</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.172846</v>
+        <v>-0.172846</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.919814</v>
+        <v>-0.919814</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.496136</v>
+        <v>-2.496136</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.813302</v>
+        <v>-1.813302</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.442481</v>
+        <v>-2.442481</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.384723</v>
+        <v>-1.384723</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.648234</v>
+        <v>-1.648234</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2.003025</v>
+        <v>-2.003025</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2.416189</v>
+        <v>-2.416189</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.911632</v>
+        <v>-1.911632</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.684791</v>
+        <v>-0.684791</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-4.764727</v>
@@ -1926,37 +1926,37 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-8.642300000000001</v>
+        <v>8.642300000000001</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-18.39628</v>
+        <v>18.39628</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-22.692145</v>
+        <v>22.692145</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-30.2217</v>
+        <v>30.2217</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-34.892586</v>
+        <v>34.892586</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-46.157433</v>
+        <v>46.157433</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-54.941133</v>
+        <v>54.941133</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-66.7675</v>
+        <v>66.7675</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-80.53963299999999</v>
+        <v>80.53963299999999</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-11.244894</v>
+        <v>11.244894</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-13.69582</v>
+        <v>13.69582</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>0.641282</v>
@@ -1981,40 +1981,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.058988</v>
+        <v>-0.058988</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.172846</v>
+        <v>-0.172846</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.919814</v>
+        <v>-0.919814</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.496136</v>
+        <v>-2.496136</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.813302</v>
+        <v>-1.813302</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.442481</v>
+        <v>-2.442481</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.384723</v>
+        <v>-1.384723</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.648234</v>
+        <v>-1.648234</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.003025</v>
+        <v>-2.003025</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.416189</v>
+        <v>-2.416189</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.911632</v>
+        <v>-1.911632</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.684791</v>
+        <v>-0.684791</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-4.764727</v>
@@ -2097,40 +2097,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.058988</v>
+        <v>-0.058988</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.172846</v>
+        <v>-0.172846</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.919814</v>
+        <v>-0.919814</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.496136</v>
+        <v>-2.496136</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.813302</v>
+        <v>-1.813302</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.442481</v>
+        <v>-2.442481</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.384723</v>
+        <v>-1.384723</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.648234</v>
+        <v>-1.648234</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.003025</v>
+        <v>-2.003025</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.416189</v>
+        <v>-2.416189</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.911632</v>
+        <v>-1.911632</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.684791</v>
+        <v>-0.684791</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-4.764727</v>
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>75083.73919874313</v>
+        <v>-75083.73919874313</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>9115.96112886049</v>
+        <v>-9115.96112886049</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>-158454.5061523113</v>
@@ -2239,40 +2239,40 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>75083.73919874313</v>
+        <v>-75083.73919874313</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>9115.96112886049</v>
+        <v>-9115.96112886049</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>-158454.5061523113</v>
@@ -39090,19 +39090,19 @@
         </is>
       </c>
       <c r="L306" s="5" t="n">
-        <v>1.648234</v>
+        <v>-1.648234</v>
       </c>
       <c r="M306" s="5" t="n">
-        <v>2.003025</v>
+        <v>-2.003025</v>
       </c>
       <c r="N306" s="5" t="n">
-        <v>2.416189</v>
+        <v>-2.416189</v>
       </c>
       <c r="O306" s="5" t="n">
-        <v>1.911632</v>
+        <v>-1.911632</v>
       </c>
       <c r="P306" s="5" t="n">
-        <v>0.684791</v>
+        <v>-0.684791</v>
       </c>
       <c r="Q306" t="inlineStr">
         <is>
@@ -39955,13 +39955,13 @@
         </is>
       </c>
       <c r="J315" s="5" t="n">
-        <v>2.442481</v>
+        <v>-2.442481</v>
       </c>
       <c r="K315" s="5" t="n">
-        <v>1.384723</v>
+        <v>-1.384723</v>
       </c>
       <c r="L315" s="5" t="n">
-        <v>1.648234</v>
+        <v>-1.648234</v>
       </c>
       <c r="M315" t="inlineStr">
         <is>
@@ -41624,13 +41624,13 @@
         </is>
       </c>
       <c r="H332" s="5" t="n">
-        <v>2.496136</v>
+        <v>-2.496136</v>
       </c>
       <c r="I332" s="5" t="n">
-        <v>1.813302</v>
+        <v>-1.813302</v>
       </c>
       <c r="J332" s="5" t="n">
-        <v>2.442481</v>
+        <v>-2.442481</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
@@ -43547,10 +43547,10 @@
         </is>
       </c>
       <c r="F351" s="5" t="n">
-        <v>0.172846</v>
+        <v>-0.172846</v>
       </c>
       <c r="G351" s="5" t="n">
-        <v>0.919814</v>
+        <v>-0.919814</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
@@ -44251,10 +44251,10 @@
         </is>
       </c>
       <c r="E358" s="5" t="n">
-        <v>0.058988</v>
+        <v>-0.058988</v>
       </c>
       <c r="F358" s="5" t="n">
-        <v>0.172846</v>
+        <v>-0.172846</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MKT.xlsx
+++ b/output/pdf_financials_xlsx/MKT.xlsx
@@ -957,19 +957,19 @@
         <v>0.692303</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.033391</v>
+        <v>4.767734</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.085591</v>
+        <v>6.209241</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.082991</v>
+        <v>9.496433</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.036952</v>
+        <v>0.7992359999999999</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.03649</v>
+        <v>0.239992</v>
       </c>
     </row>
     <row r="11">
@@ -1017,10 +1017,10 @@
         <v>-0.684791</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.030384</v>
+        <v>-4.764727</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.085082</v>
+        <v>-6.208732</v>
       </c>
       <c r="P11" s="1" t="inlineStr">
         <is>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.036952</v>
+        <v>-0.7992359999999999</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.03649</v>
+        <v>-0.239992</v>
       </c>
     </row>
     <row r="12">
@@ -1041,40 +1041,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00796</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003642</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001574</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006264</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002518</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003061</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001878</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003911</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001713</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006195</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009819</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002808</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1083,10 +1083,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006923</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001628</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -1981,40 +1981,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.058988</v>
+        <v>-0.051028</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.172846</v>
+        <v>-0.169204</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.919814</v>
+        <v>-0.9182399999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.496136</v>
+        <v>-2.489872</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.813302</v>
+        <v>-1.810784</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.442481</v>
+        <v>-2.43942</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.384723</v>
+        <v>-1.382845</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.648234</v>
+        <v>-1.644323</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.003025</v>
+        <v>-2.001312</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.416189</v>
+        <v>-2.409994</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.911632</v>
+        <v>-1.901813</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.684791</v>
+        <v>-0.681983</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-4.764727</v>
@@ -2023,10 +2023,10 @@
         <v>-6.208732</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-9.496433</v>
+        <v>-9.489509999999999</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.7992359999999999</v>
+        <v>-0.797608</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-0.239992</v>
@@ -2097,40 +2097,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.058988</v>
+        <v>-0.051028</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.172846</v>
+        <v>-0.169204</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.919814</v>
+        <v>-0.9182399999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.496136</v>
+        <v>-2.489872</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.813302</v>
+        <v>-1.810784</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.442481</v>
+        <v>-2.43942</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.384723</v>
+        <v>-1.382845</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.648234</v>
+        <v>-1.644323</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.003025</v>
+        <v>-2.001312</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.416189</v>
+        <v>-2.409994</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.911632</v>
+        <v>-1.901813</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.684791</v>
+        <v>-0.681983</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-4.764727</v>
@@ -2139,10 +2139,10 @@
         <v>-6.208732</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-9.496433</v>
+        <v>-9.489509999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.7992359999999999</v>
+        <v>-0.797608</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-0.239992</v>
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-75083.73919874313</v>
+        <v>-74698.07541241164</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-9115.96112886049</v>
+        <v>-9078.580937167198</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>-158454.5061523113</v>
@@ -7910,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>0</v>
@@ -22737,7 +22737,11 @@
           <t>Short-term lease payments</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -33519,7 +33523,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -35212,7 +35216,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -36113,7 +36117,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -38665,7 +38669,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E302" s="5" t="n">
@@ -43435,7 +43439,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">

--- a/output/pdf_financials_xlsx/MKT.xlsx
+++ b/output/pdf_financials_xlsx/MKT.xlsx
@@ -7205,10 +7205,10 @@
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.00112</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="N112" s="3" t="n">
         <v>0</v>
@@ -22943,7 +22943,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -23436,7 +23440,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MKT.xlsx
+++ b/output/pdf_financials_xlsx/MKT.xlsx
@@ -7159,7 +7159,7 @@
         <v>0</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001523</v>
       </c>
       <c r="Q111" s="3" t="n">
         <v>0</v>
@@ -7446,10 +7446,10 @@
         <v>0</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.3127</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-0.2975</v>
       </c>
       <c r="Q116" s="3" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>0</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001523</v>
       </c>
       <c r="Q134" s="3" t="n">
         <v>0</v>
@@ -8615,7 +8615,7 @@
         <v>-2.58313</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-1.561137</v>
+        <v>-1.56266</v>
       </c>
       <c r="Q135" s="3" t="n">
         <v>-0.348924</v>
@@ -19850,7 +19850,11 @@
           <t>Purchase of equipment 4</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -19951,7 +19955,11 @@
           <t>Purchase of intangible assets 4</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -21656,7 +21664,11 @@
           <t>Purchase of equipment 5</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -21757,7 +21769,11 @@
           <t>Purchase of intangible assets 6</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
